--- a/Design Files/Xponent-tech/BOM/JLCPCB-BOM-Xponent-tech.xlsx
+++ b/Design Files/Xponent-tech/BOM/JLCPCB-BOM-Xponent-tech.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="169">
   <si>
     <t>Comment</t>
   </si>
@@ -219,13 +219,13 @@
     <t>MK1</t>
   </si>
   <si>
-    <t>R1, R10, R67</t>
+    <t>R1, R10</t>
   </si>
   <si>
     <t>R2, R3, R4, R7, R8, R9, R48, R52, R65, R66, R68, R69, R70</t>
   </si>
   <si>
-    <t>R5, R14</t>
+    <t>R5</t>
   </si>
   <si>
     <t>R6, R42, R43, R58</t>
@@ -237,6 +237,9 @@
     <t>R13</t>
   </si>
   <si>
+    <t>R14</t>
+  </si>
+  <si>
     <t>R15, R16</t>
   </si>
   <si>
@@ -306,6 +309,9 @@
     <t>R64</t>
   </si>
   <si>
+    <t>R67</t>
+  </si>
+  <si>
     <t>R71, R72</t>
   </si>
   <si>
@@ -345,21 +351,24 @@
     <t>ZTS6117_</t>
   </si>
   <si>
+    <t>3296W_</t>
+  </si>
+  <si>
+    <t>Res-0603</t>
+  </si>
+  <si>
+    <t>VG039NCHXTB504_</t>
+  </si>
+  <si>
+    <t>RES-0805</t>
+  </si>
+  <si>
+    <t>Res-0402</t>
+  </si>
+  <si>
     <t>TC33X-2-104E_</t>
   </si>
   <si>
-    <t>Res-0603</t>
-  </si>
-  <si>
-    <t>VG039NCHXTB504_</t>
-  </si>
-  <si>
-    <t>RES-0805</t>
-  </si>
-  <si>
-    <t>Res-0402</t>
-  </si>
-  <si>
     <t>DSIC05LS-P_</t>
   </si>
   <si>
@@ -402,99 +411,108 @@
     <t>C481300</t>
   </si>
   <si>
+    <t>C330435</t>
+  </si>
+  <si>
+    <t>C95204</t>
+  </si>
+  <si>
+    <t>C128558</t>
+  </si>
+  <si>
+    <t>C110776</t>
+  </si>
+  <si>
+    <t>C309653</t>
+  </si>
+  <si>
+    <t>C469656</t>
+  </si>
+  <si>
+    <t>C330437</t>
+  </si>
+  <si>
+    <t>C705745</t>
+  </si>
+  <si>
+    <t>C705836</t>
+  </si>
+  <si>
+    <t>C3014409</t>
+  </si>
+  <si>
+    <t>C5266069</t>
+  </si>
+  <si>
+    <t>C5266105</t>
+  </si>
+  <si>
+    <t>C319766</t>
+  </si>
+  <si>
+    <t>C327136</t>
+  </si>
+  <si>
+    <t>C861589</t>
+  </si>
+  <si>
+    <t>C137968</t>
+  </si>
+  <si>
+    <t>C114612</t>
+  </si>
+  <si>
+    <t>C318130</t>
+  </si>
+  <si>
+    <t>C852616</t>
+  </si>
+  <si>
+    <t>C2984321</t>
+  </si>
+  <si>
+    <t>C705736</t>
+  </si>
+  <si>
+    <t>C2828704</t>
+  </si>
+  <si>
+    <t>C852922</t>
+  </si>
+  <si>
+    <t>C861117</t>
+  </si>
+  <si>
+    <t>C2933514</t>
+  </si>
+  <si>
+    <t>C865602</t>
+  </si>
+  <si>
+    <t>C2684524</t>
+  </si>
+  <si>
+    <t>C2828711</t>
+  </si>
+  <si>
+    <t>C852794</t>
+  </si>
+  <si>
+    <t>C2683044</t>
+  </si>
+  <si>
     <t>C719186</t>
   </si>
   <si>
-    <t>C95204</t>
-  </si>
-  <si>
-    <t>C128558</t>
-  </si>
-  <si>
-    <t>C110776</t>
-  </si>
-  <si>
-    <t>C309653</t>
-  </si>
-  <si>
-    <t>C469656</t>
-  </si>
-  <si>
-    <t>C705745</t>
-  </si>
-  <si>
-    <t>C705836</t>
-  </si>
-  <si>
-    <t>C3014409</t>
-  </si>
-  <si>
-    <t>C5266069</t>
-  </si>
-  <si>
-    <t>C5266105</t>
-  </si>
-  <si>
-    <t>C319766</t>
-  </si>
-  <si>
-    <t>C327136</t>
-  </si>
-  <si>
-    <t>C861589</t>
-  </si>
-  <si>
-    <t>C137968</t>
-  </si>
-  <si>
-    <t>C114612</t>
-  </si>
-  <si>
-    <t>C318130</t>
-  </si>
-  <si>
-    <t>C852616</t>
-  </si>
-  <si>
-    <t>C2984321</t>
-  </si>
-  <si>
-    <t>C705736</t>
-  </si>
-  <si>
-    <t>C2828704</t>
-  </si>
-  <si>
-    <t>C852922</t>
-  </si>
-  <si>
-    <t>C861117</t>
-  </si>
-  <si>
-    <t>C2933514</t>
-  </si>
-  <si>
-    <t>C865602</t>
-  </si>
-  <si>
-    <t>C2684524</t>
-  </si>
-  <si>
-    <t>C2828711</t>
-  </si>
-  <si>
-    <t>C852794</t>
-  </si>
-  <si>
-    <t>C2683044</t>
-  </si>
-  <si>
     <t>C326725</t>
   </si>
   <si>
     <t>C319036</t>
   </si>
   <si>
+    <t>C105411</t>
+  </si>
+  <si>
     <t>C525277</t>
   </si>
   <si>
@@ -508,9 +526,6 @@
   </si>
   <si>
     <t>C387979</t>
-  </si>
-  <si>
-    <t>C105411</t>
   </si>
 </sst>
 </file>
@@ -956,7 +971,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -973,10 +988,10 @@
         <v>48</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -987,10 +1002,10 @@
         <v>49</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1001,10 +1016,10 @@
         <v>50</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1015,10 +1030,10 @@
         <v>51</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1029,10 +1044,10 @@
         <v>52</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1043,10 +1058,10 @@
         <v>53</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1057,10 +1072,10 @@
         <v>54</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1071,10 +1086,10 @@
         <v>55</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1085,10 +1100,10 @@
         <v>56</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1099,10 +1114,10 @@
         <v>57</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1113,10 +1128,10 @@
         <v>58</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1127,10 +1142,10 @@
         <v>59</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1141,10 +1156,10 @@
         <v>60</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1155,10 +1170,10 @@
         <v>61</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1169,10 +1184,10 @@
         <v>62</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1183,10 +1198,10 @@
         <v>63</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1197,7 +1212,7 @@
         <v>64</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>14</v>
@@ -1211,10 +1226,10 @@
         <v>65</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1225,10 +1240,10 @@
         <v>66</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1239,10 +1254,10 @@
         <v>67</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1253,10 +1268,10 @@
         <v>68</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1267,10 +1282,10 @@
         <v>69</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1281,10 +1296,10 @@
         <v>70</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1295,57 +1310,57 @@
         <v>71</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>72</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>75</v>
@@ -1354,152 +1369,152 @@
         <v>111</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>77</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>80</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>81</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>82</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>84</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>85</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>86</v>
@@ -1508,40 +1523,40 @@
         <v>111</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>88</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>89</v>
@@ -1550,118 +1565,146 @@
         <v>111</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>90</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>94</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>95</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+      <c r="B51" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" s="6" t="s">
+      <c r="B52" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D52" s="6" t="s">
         <v>163</v>
       </c>
     </row>
